--- a/artfynd/A 1672-2024 artfynd.xlsx
+++ b/artfynd/A 1672-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1672-2024 artfynd.xlsx
+++ b/artfynd/A 1672-2024 artfynd.xlsx
@@ -2768,10 +2768,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117400120</v>
+        <v>117400118</v>
       </c>
       <c r="B22" t="n">
-        <v>78216</v>
+        <v>91962</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2784,21 +2784,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588430</v>
+        <v>588418</v>
       </c>
       <c r="R22" t="n">
-        <v>7027598</v>
+        <v>7027603</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2870,10 +2870,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117400118</v>
+        <v>117400120</v>
       </c>
       <c r="B23" t="n">
-        <v>91962</v>
+        <v>78216</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2886,21 +2886,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2910,10 +2910,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588418</v>
+        <v>588430</v>
       </c>
       <c r="R23" t="n">
-        <v>7027603</v>
+        <v>7027598</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>

--- a/artfynd/A 1672-2024 artfynd.xlsx
+++ b/artfynd/A 1672-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3077,6 +3077,4551 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>118135188</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90784</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>658</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>588428</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7027314</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>118135209</v>
+      </c>
+      <c r="B26" t="n">
+        <v>90519</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>588463</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7027227</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>118135201</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78218</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>588449</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7027364</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>118135221</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91774</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>588181</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7027372</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>118135217</v>
+      </c>
+      <c r="B29" t="n">
+        <v>82261</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>588404</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7027440</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>118135223</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91774</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>588434</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7027505</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>118135381</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57288</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>588463</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7027368</v>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>118135162</v>
+      </c>
+      <c r="B32" t="n">
+        <v>90501</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>588465</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7027249</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>118135178</v>
+      </c>
+      <c r="B33" t="n">
+        <v>90521</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>588508</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7027395</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>118135182</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79100</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>588392</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7027369</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>118135195</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91797</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>588405</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7027515</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>118135215</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78482</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>588528</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7027451</v>
+      </c>
+      <c r="S36" t="n">
+        <v>20</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>118135379</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57288</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>588399</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7027693</v>
+      </c>
+      <c r="S37" t="n">
+        <v>20</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>118135218</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78127</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>353</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>588401</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7027539</v>
+      </c>
+      <c r="S38" t="n">
+        <v>20</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>118135224</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91774</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>588411</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7027647</v>
+      </c>
+      <c r="S39" t="n">
+        <v>20</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>118135163</v>
+      </c>
+      <c r="B40" t="n">
+        <v>90501</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>588470</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7027219</v>
+      </c>
+      <c r="S40" t="n">
+        <v>20</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>118135183</v>
+      </c>
+      <c r="B41" t="n">
+        <v>90943</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>588290</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7027315</v>
+      </c>
+      <c r="S41" t="n">
+        <v>20</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>118135160</v>
+      </c>
+      <c r="B42" t="n">
+        <v>90501</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>588448</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7027260</v>
+      </c>
+      <c r="S42" t="n">
+        <v>20</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>118135192</v>
+      </c>
+      <c r="B43" t="n">
+        <v>90784</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>658</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>588463</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7027223</v>
+      </c>
+      <c r="S43" t="n">
+        <v>20</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>118135181</v>
+      </c>
+      <c r="B44" t="n">
+        <v>91197</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>67</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Sprickporing</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Diplomitoporus crustulinus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>588468</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7027225</v>
+      </c>
+      <c r="S44" t="n">
+        <v>20</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>118135158</v>
+      </c>
+      <c r="B45" t="n">
+        <v>90501</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>588428</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7027314</v>
+      </c>
+      <c r="S45" t="n">
+        <v>20</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>118135189</v>
+      </c>
+      <c r="B46" t="n">
+        <v>90784</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>658</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>588429</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7027338</v>
+      </c>
+      <c r="S46" t="n">
+        <v>20</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>118135207</v>
+      </c>
+      <c r="B47" t="n">
+        <v>56492</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>588368</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7027370</v>
+      </c>
+      <c r="S47" t="n">
+        <v>20</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>118135152</v>
+      </c>
+      <c r="B48" t="n">
+        <v>90843</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>588305</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7027322</v>
+      </c>
+      <c r="S48" t="n">
+        <v>20</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>118135380</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57288</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>588376</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7027714</v>
+      </c>
+      <c r="S49" t="n">
+        <v>20</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>118135187</v>
+      </c>
+      <c r="B50" t="n">
+        <v>90784</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>658</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>588375</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7027377</v>
+      </c>
+      <c r="S50" t="n">
+        <v>20</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>118135191</v>
+      </c>
+      <c r="B51" t="n">
+        <v>90784</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>658</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>588479</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7027224</v>
+      </c>
+      <c r="S51" t="n">
+        <v>20</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>118135208</v>
+      </c>
+      <c r="B52" t="n">
+        <v>56492</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>588398</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7027359</v>
+      </c>
+      <c r="S52" t="n">
+        <v>20</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>118135184</v>
+      </c>
+      <c r="B53" t="n">
+        <v>90943</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>588441</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7027297</v>
+      </c>
+      <c r="S53" t="n">
+        <v>20</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>118135161</v>
+      </c>
+      <c r="B54" t="n">
+        <v>90501</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>588457</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7027260</v>
+      </c>
+      <c r="S54" t="n">
+        <v>20</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>118135156</v>
+      </c>
+      <c r="B55" t="n">
+        <v>90501</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>588375</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7027377</v>
+      </c>
+      <c r="S55" t="n">
+        <v>20</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>118135214</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78482</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>588403</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7027448</v>
+      </c>
+      <c r="S56" t="n">
+        <v>20</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>118135177</v>
+      </c>
+      <c r="B57" t="n">
+        <v>56500</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>588434</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7027505</v>
+      </c>
+      <c r="S57" t="n">
+        <v>20</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>118135216</v>
+      </c>
+      <c r="B58" t="n">
+        <v>78482</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>588290</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7027315</v>
+      </c>
+      <c r="S58" t="n">
+        <v>20</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>118135151</v>
+      </c>
+      <c r="B59" t="n">
+        <v>90466</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>588516</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7027388</v>
+      </c>
+      <c r="S59" t="n">
+        <v>20</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>118135222</v>
+      </c>
+      <c r="B60" t="n">
+        <v>91774</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>588403</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7027519</v>
+      </c>
+      <c r="S60" t="n">
+        <v>20</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>118135382</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57288</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>588399</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7027366</v>
+      </c>
+      <c r="S61" t="n">
+        <v>20</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>118135185</v>
+      </c>
+      <c r="B62" t="n">
+        <v>90784</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>658</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>588376</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7027380</v>
+      </c>
+      <c r="S62" t="n">
+        <v>20</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>118135190</v>
+      </c>
+      <c r="B63" t="n">
+        <v>90784</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>658</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>588458</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7027246</v>
+      </c>
+      <c r="S63" t="n">
+        <v>20</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>118135155</v>
+      </c>
+      <c r="B64" t="n">
+        <v>90501</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>588296</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7027314</v>
+      </c>
+      <c r="S64" t="n">
+        <v>20</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>118135159</v>
+      </c>
+      <c r="B65" t="n">
+        <v>90501</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>588429</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7027338</v>
+      </c>
+      <c r="S65" t="n">
+        <v>20</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>118135176</v>
+      </c>
+      <c r="B66" t="n">
+        <v>56500</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>588401</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7027539</v>
+      </c>
+      <c r="S66" t="n">
+        <v>20</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>118135383</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57288</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>588423</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7027330</v>
+      </c>
+      <c r="S67" t="n">
+        <v>20</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>118135213</v>
+      </c>
+      <c r="B68" t="n">
+        <v>78482</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>588352</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7027378</v>
+      </c>
+      <c r="S68" t="n">
+        <v>20</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
